--- a/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N76_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1929_W0014F0002T0006Z000C1N76_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>24.00220684392294</v>
+        <v>3.900358612137477</v>
       </c>
       <c r="D2" t="n">
-        <v>23.21021596932903</v>
+        <v>3.771660095015967</v>
       </c>
       <c r="E2" t="n">
-        <v>11.80021321748615</v>
+        <v>1.9175346478415</v>
       </c>
       <c r="F2" t="n">
-        <v>10.06854353146173</v>
+        <v>1.636138323862531</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>40.30649084029554</v>
+        <v>6.549804761548025</v>
       </c>
       <c r="D3" t="n">
-        <v>14.00342118871892</v>
+        <v>2.275555943166825</v>
       </c>
       <c r="E3" t="n">
-        <v>11.80021321748615</v>
+        <v>1.9175346478415</v>
       </c>
       <c r="F3" t="n">
-        <v>10.06854353146173</v>
+        <v>1.636138323862531</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.67576823419979</v>
+        <v>4.984812338057466</v>
       </c>
       <c r="D4" t="n">
-        <v>3.30952380952381</v>
+        <v>0.5377976190476191</v>
       </c>
       <c r="E4" t="n">
-        <v>11.80021321748615</v>
+        <v>1.9175346478415</v>
       </c>
       <c r="F4" t="n">
-        <v>10.06854353146173</v>
+        <v>1.636138323862531</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>6.194311085671272</v>
+        <v>1.006575551421582</v>
       </c>
       <c r="D5" t="n">
-        <v>2.772727308555368</v>
+        <v>0.4505681876402473</v>
       </c>
       <c r="E5" t="n">
-        <v>11.80021321748615</v>
+        <v>1.9175346478415</v>
       </c>
       <c r="F5" t="n">
-        <v>10.06854353146173</v>
+        <v>1.636138323862531</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>35.00422597761673</v>
+        <v>5.688186721362718</v>
       </c>
       <c r="D6" t="n">
-        <v>27.48457059986373</v>
+        <v>4.466242722477856</v>
       </c>
       <c r="E6" t="n">
-        <v>11.80021321748615</v>
+        <v>1.9175346478415</v>
       </c>
       <c r="F6" t="n">
-        <v>10.06854353146173</v>
+        <v>1.636138323862531</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
